--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/mobile/mobile_search_visibility.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/mobile/mobile_search_visibility.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C2" t="n">
-        <v>39.5</v>
+        <v>40.18</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C4" t="n">
-        <v>27.5</v>
+        <v>27.68</v>
       </c>
     </row>
   </sheetData>
